--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:25</t>
+    <t xml:space="preserve">2026-09-09 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -45,6 +45,9 @@
     <t xml:space="preserve">Combarbalá</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:22</t>
+    <t xml:space="preserve">2026-09-17 14:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -568,13 +568,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4305</v>
+        <v>4105</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>22.07</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="6">
@@ -585,13 +585,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4202</v>
+        <v>4305</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>21.82</v>
+        <v>22.07</v>
       </c>
     </row>
     <row r="7">
@@ -602,13 +602,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4301</v>
+        <v>4202</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.14</v>
+        <v>21.82</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.83</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="9">
@@ -636,13 +636,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4203</v>
+        <v>4304</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>17.87</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="10">
@@ -653,13 +653,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>17.41</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4104</v>
+        <v>4204</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16.3</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="12">
@@ -684,16 +684,16 @@
         <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4102</v>
+        <v>4104</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>15.4</v>
+        <v>16.3</v>
       </c>
     </row>
     <row r="13">
@@ -701,16 +701,16 @@
         <v>5</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4201</v>
+        <v>4102</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>14.72</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="14">
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4101</v>
+        <v>4201</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13.63</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4103</v>
+        <v>4101</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>11.61</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4103</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>11.61</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:17</t>
+    <t xml:space="preserve">2026-09-23 12:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:45</t>
+    <t xml:space="preserve">2026-10-01 23:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -841,7 +838,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:03</t>
+    <t xml:space="preserve">2026-10-02 11:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:18</t>
+    <t xml:space="preserve">2026-10-02 14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:16</t>
+    <t xml:space="preserve">2026-10-04 09:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2019_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:19</t>
+    <t xml:space="preserve">2026-10-05 11:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
